--- a/Vulnerability Test Results/findings.xlsx
+++ b/Vulnerability Test Results/findings.xlsx
@@ -35,7 +35,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -44,8 +44,32 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001E3A8A"/>
-        <bgColor rgb="001E3A8A"/>
+        <fgColor rgb="001A365D"/>
+        <bgColor rgb="001A365D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00ECFDF5"/>
+        <bgColor rgb="00ECFDF5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF3C7"/>
+        <bgColor rgb="00FEF3C7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEE2E2"/>
+        <bgColor rgb="00FEE2E2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFEDD5"/>
+        <bgColor rgb="00FFEDD5"/>
       </patternFill>
     </fill>
   </fills>
@@ -59,29 +83,41 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00DDDDDD"/>
+        <color rgb="00E2E8F0"/>
       </left>
       <right style="thin">
-        <color rgb="00DDDDDD"/>
+        <color rgb="00E2E8F0"/>
       </right>
       <top style="thin">
-        <color rgb="00DDDDDD"/>
+        <color rgb="00E2E8F0"/>
       </top>
       <bottom style="thin">
-        <color rgb="00DDDDDD"/>
+        <color rgb="00E2E8F0"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -448,16 +484,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="19" customWidth="1" min="1" max="1"/>
+    <col width="21" customWidth="1" min="1" max="1"/>
     <col width="11" customWidth="1" min="2" max="2"/>
     <col width="43" customWidth="1" min="3" max="3"/>
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="26" customWidth="1" min="5" max="5"/>
-    <col width="200" customWidth="1" min="6" max="6"/>
-    <col width="145" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -500,185 +536,259 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SEC-FIND-PHP-001</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Critical</t>
+          <t>SEC-ERR-DB_CONNECT</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Broken Object Level Authorization (BOLA)</t>
+          <t>Verbose Error Message Leakage</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>endo_backend_/get_patients.php</t>
+          <t>endo_backend_/db_connect.php</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>/get_patients.php (GET)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Missing authentication and authorization validations. The patient details endpoint returns medical data directly to any unauthorized client making a query.</t>
+          <t>Verbose server-side database details or error strings are returned directly to the client payload.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>Require session tokens or JWT authentication headers, and ensure only authenticated doctors associated with the record can read patient files.</t>
+          <t>Log verbose error context to server logs and return sanitized HTTP responses to public clients.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>SEC-FIND-PHP-002</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>SEC-CRED-DB</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Medium</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>SQL Injection (SQLi)</t>
+          <t>Hardcoded Configuration Credentials</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>endo_backend_/login.php</t>
+          <t>endo_backend_/db_connect.php</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>/login.php (POST)</t>
+          <t>None</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>The SQL query concatenates `$email` parameters directly inside the query string. Although escaping is done, it is vulnerable to SQL injection bypasses depending on database encoding configurations.</t>
+          <t>The configuration file defines root database login details with no password explicitly inside the script file.</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>Implement prepared statements with parameterized queries instead of variable interpolation.</t>
+          <t>Load credentials from environment variables (`$_ENV`) rather than hardcoding them in files.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>SEC-FIND-PHP-003</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
+          <t>SEC-BOLA-PATIENTS</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>Critical</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>SQL Injection (SQLi)</t>
+          <t>Broken Object Level Authorization (BOLA)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>endo_backend_/register.php</t>
+          <t>endo_backend_/get_patients.php</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>/register.php (POST)</t>
+          <t>/get_patients.php (GET)</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>The registration logic directly inserts user inputs into database variables via string interpolation.</t>
+          <t>Missing authentication check and access control validations. Patient information is fetched from database and returned without validating token authorization headers.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>Implement prepared statements using PHP's PDO or MySQLi parameterized query bindings.</t>
+          <t>Require session tokens or JWT authentication headers, and ensure only authenticated doctors associated with the record can read patient files.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>SEC-FIND-PHP-004</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
+          <t>SEC-SQLI-LOGIN</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Sensitive Information Disclosure</t>
+          <t>SQL Injection (SQLi)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>endo_backend_/register.php</t>
+          <t>endo_backend_/login.php</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>/register.php (POST)</t>
+          <t>/login.php (POST)</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Verbose database error information is returned directly to the client in the API payload response on failure (using `$conn-&gt;error`).</t>
+          <t>The query constructed in login.php inserts variables directly into the query string via interpolation. This allows parameter manipulation.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>Log errors securely to server files and return generic HTTP error responses (e.g. 'Internal Server Error') to the user.</t>
+          <t>Use prepared statements with parameterized input bindings via mysqli or PDO.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SEC-FIND-PHP-005</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
+          <t>SEC-DISC-LOGIN</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Username Enumeration</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>endo_backend_/login.php</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>/login.php (POST)</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>The authentication script returns distinct responses ('User not found' vs 'Invalid password') based on existence of the user profile.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Return a generic validation message (e.g., 'Invalid email or password') for both missing users and password mismatches.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>SEC-SQLI-REGISTER</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>SQL Injection (SQLi)</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>endo_backend_/register.php</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>/register.php (POST)</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>The query constructed in register.php inserts variables directly into the query string via interpolation. This allows parameter manipulation.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Use prepared statements with parameterized input bindings via mysqli or PDO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>SEC-ERR-REGISTER</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Hardcoded Cleartext Credentials</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>endo_backend_/db_connect.php</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>The configuration file defines root database login details with no password explicitly inside the script file.</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Load credentials from environment variables (`$_ENV`) rather than hardcoding them in files.</t>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Verbose Error Message Leakage</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>endo_backend_/register.php</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>/register.php (POST)</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Verbose server-side database details or error strings are returned directly to the client payload.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Log verbose error context to server logs and return sanitized HTTP responses to public clients.</t>
         </is>
       </c>
     </row>
@@ -693,7 +803,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -733,12 +843,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>/register.php</t>
+          <t>/db_connect.php</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -753,19 +863,19 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>endo_backend_/register.php</t>
+          <t>endo_backend_/db_connect.php</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>/login.php</t>
+          <t>/get_patients.php</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>POST</t>
+          <t>GET</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -780,19 +890,19 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>endo_backend_/login.php</t>
+          <t>endo_backend_/get_patients.php</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>/get_patients.php</t>
+          <t>/login.php</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>GET</t>
+          <t>POST</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -807,7 +917,34 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>endo_backend_/get_patients.php</t>
+          <t>endo_backend_/login.php</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>/register.php</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Guest/Any</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>endo_backend_/register.php</t>
         </is>
       </c>
     </row>
@@ -830,7 +967,7 @@
     <col width="11" customWidth="1" min="3" max="3"/>
     <col width="17" customWidth="1" min="4" max="4"/>
     <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="71" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -998,7 +1135,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3">
@@ -1038,7 +1175,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -1049,7 +1186,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>45/100</t>
+          <t>23/100</t>
         </is>
       </c>
     </row>
